--- a/master/result/98_重生商海_破浪前行/98_重生商海_破浪前行.xlsx
+++ b/master/result/98_重生商海_破浪前行/98_重生商海_破浪前行.xlsx
@@ -397,445 +397,563 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:D39"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>moon</v>
       </c>
       <c r="B2" t="str">
-        <v>moon</v>
+        <v>/moon/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>月亮</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>decision</v>
       </c>
       <c r="B3" t="str">
-        <v>decision</v>
+        <v>/decision/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>决定</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>order</v>
       </c>
       <c r="B4" t="str">
-        <v>order</v>
+        <v>/ˈɔːdə/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>订单</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>big</v>
       </c>
       <c r="B5" t="str">
-        <v>big</v>
+        <v>/big/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>大</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>aim</v>
       </c>
       <c r="B6" t="str">
-        <v>aim</v>
+        <v>/aim/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>目的</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>cease</v>
       </c>
       <c r="B7" t="str">
-        <v>cease</v>
+        <v>/cease/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>停止</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>tower</v>
       </c>
       <c r="B8" t="str">
-        <v>tower</v>
+        <v>/tower/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>塔</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>summary</v>
       </c>
       <c r="B9" t="str">
-        <v>summary</v>
+        <v>/summary/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>摘要</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>intensive</v>
       </c>
       <c r="B10" t="str">
+        <v>/intensive/</v>
+      </c>
+      <c r="C10" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>集中的</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>prosperity</v>
+      </c>
+      <c r="B11" t="str">
+        <v>/prosperity/</v>
+      </c>
+      <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>繁荣</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>negotiate</v>
+      </c>
+      <c r="B12" t="str">
+        <v>/nɪˈɡəʊʃieɪt/</v>
+      </c>
+      <c r="C12" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>谈判</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>systematic</v>
+      </c>
+      <c r="B13" t="str">
+        <v>/systematic/</v>
+      </c>
+      <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>系统的</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>bar</v>
+      </c>
+      <c r="B14" t="str">
+        <v>/bar/</v>
+      </c>
+      <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>酒吧</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>hear</v>
+      </c>
+      <c r="B15" t="str">
+        <v>/hɪə/</v>
+      </c>
+      <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>听</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>foundation</v>
+      </c>
+      <c r="B16" t="str">
+        <v>/foundation/</v>
+      </c>
+      <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>基础</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>initiate</v>
+      </c>
+      <c r="B17" t="str">
+        <v>/initiate/</v>
+      </c>
+      <c r="C17" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>开始</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>intensive</v>
       </c>
-      <c r="C10" t="str">
-        <v>集中的</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>prosperity</v>
-      </c>
-      <c r="C11" t="str">
-        <v>繁荣</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>negotiate</v>
-      </c>
-      <c r="C12" t="str">
-        <v>谈判</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>systematic</v>
-      </c>
-      <c r="C13" t="str">
-        <v>系统的</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>bar</v>
-      </c>
-      <c r="C14" t="str">
-        <v>酒吧</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="str">
-        <v>hear</v>
-      </c>
-      <c r="C15" t="str">
-        <v>听</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
+      <c r="B18" t="str">
+        <v>/intensive/</v>
+      </c>
+      <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>深入的</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>wholesome</v>
+      </c>
+      <c r="B19" t="str">
+        <v>/wholesome/</v>
+      </c>
+      <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>健康的</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>item</v>
+      </c>
+      <c r="B20" t="str">
+        <v>/item/</v>
+      </c>
+      <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>项目</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>refine</v>
+      </c>
+      <c r="B21" t="str">
+        <v>/refine/</v>
+      </c>
+      <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>精制</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>tiresome</v>
+      </c>
+      <c r="B22" t="str">
+        <v>/tiresome/</v>
+      </c>
+      <c r="C22" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>令人厌倦的</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>idiom</v>
+      </c>
+      <c r="B23" t="str">
+        <v>/idiom/</v>
+      </c>
+      <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>习语</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>river</v>
+      </c>
+      <c r="B24" t="str">
+        <v>/river/</v>
+      </c>
+      <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>河流</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>shaft</v>
+      </c>
+      <c r="B25" t="str">
+        <v>/shaft/</v>
+      </c>
+      <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>轴</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>per</v>
+      </c>
+      <c r="B26" t="str">
+        <v>/per/</v>
+      </c>
+      <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>每</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>decorate</v>
+      </c>
+      <c r="B27" t="str">
+        <v>/ˈdekəreɪt/</v>
+      </c>
+      <c r="C27" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>装饰</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>peasant</v>
+      </c>
+      <c r="B28" t="str">
+        <v>/peasant/</v>
+      </c>
+      <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>农民</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>donate</v>
+      </c>
+      <c r="B29" t="str">
+        <v>/donate/</v>
+      </c>
+      <c r="C29" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>捐赠</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>society</v>
+      </c>
+      <c r="B30" t="str">
+        <v>/society/</v>
+      </c>
+      <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>社会</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>cough</v>
+      </c>
+      <c r="B31" t="str">
+        <v>/kɒf/</v>
+      </c>
+      <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>咳嗽</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>everyone</v>
+      </c>
+      <c r="B32" t="str">
+        <v>/everyone/</v>
+      </c>
+      <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>每个人</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>shine</v>
+      </c>
+      <c r="B33" t="str">
+        <v>/ʃaɪn/</v>
+      </c>
+      <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>照耀</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>camp</v>
+      </c>
+      <c r="B34" t="str">
+        <v>/kæmp/</v>
+      </c>
+      <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>露营</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>tree</v>
+      </c>
+      <c r="B35" t="str">
+        <v>/tree/</v>
+      </c>
+      <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>树</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
         <v>foundation</v>
       </c>
-      <c r="C16" t="str">
-        <v>基础</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="str">
-        <v>initiate</v>
-      </c>
-      <c r="C17" t="str">
-        <v>开始</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="str">
-        <v>intensive</v>
-      </c>
-      <c r="C18" t="str">
-        <v>深入的</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>wholesome</v>
-      </c>
-      <c r="C19" t="str">
-        <v>健康的</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="str">
-        <v>item</v>
-      </c>
-      <c r="C20" t="str">
-        <v>项目</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>refine</v>
-      </c>
-      <c r="C21" t="str">
-        <v>精制</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="str">
-        <v>tiresome</v>
-      </c>
-      <c r="C22" t="str">
-        <v>令人厌倦的</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="str">
-        <v>idiom</v>
-      </c>
-      <c r="C23" t="str">
-        <v>习语</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="str">
-        <v>river</v>
-      </c>
-      <c r="C24" t="str">
-        <v>河流</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>shaft</v>
-      </c>
-      <c r="C25" t="str">
-        <v>轴</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>per</v>
-      </c>
-      <c r="C26" t="str">
-        <v>每</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>decorate</v>
-      </c>
-      <c r="C27" t="str">
-        <v>装饰</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>peasant</v>
-      </c>
-      <c r="C28" t="str">
-        <v>农民</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="str">
-        <v>donate</v>
-      </c>
-      <c r="C29" t="str">
-        <v>捐赠</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="str">
-        <v>society</v>
-      </c>
-      <c r="C30" t="str">
-        <v>社会</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>cough</v>
-      </c>
-      <c r="C31" t="str">
-        <v>咳嗽</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>everyone</v>
-      </c>
-      <c r="C32" t="str">
-        <v>每个人</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>shine</v>
-      </c>
-      <c r="C33" t="str">
-        <v>照耀</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>camp</v>
-      </c>
-      <c r="C34" t="str">
-        <v>露营</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>tree</v>
-      </c>
-      <c r="C35" t="str">
-        <v>树</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
       <c r="B36" t="str">
-        <v>foundation</v>
+        <v>/foundation/</v>
       </c>
       <c r="C36" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>基金会</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>plateau</v>
       </c>
       <c r="B37" t="str">
-        <v>plateau</v>
+        <v>/plateau/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>平稳状态</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>sailor</v>
       </c>
       <c r="B38" t="str">
-        <v>sailor</v>
+        <v>/sailor/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>水手</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>flower</v>
       </c>
       <c r="B39" t="str">
-        <v>flower</v>
+        <v>/flower/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>花</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
   </ignoredErrors>
 </worksheet>
 </file>